--- a/SUPPLIER RELATED/Phone Book BALAGAN.xlsx
+++ b/SUPPLIER RELATED/Phone Book BALAGAN.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19635" windowHeight="7500"/>
+    <workbookView windowHeight="17000"/>
   </bookViews>
   <sheets>
     <sheet name="Contact lists" sheetId="1" r:id="rId1"/>
@@ -97,7 +97,7 @@
 Estimulo malbec
 Fashion vodka
 McGuigan
-CAmpari
+Campari
 Vitral syrah
 Dona dominga
 Rose pipoli
@@ -138,7 +138,6 @@
 Jagermeister
 Grey goose
 McGuigan
-Campari
 Jim beam black / white
 Herradura
 Mancino rosso
@@ -661,10 +660,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -833,12 +832,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="Times New Roman"/>
       <charset val="0"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="Times New Roman"/>
       <charset val="0"/>
@@ -1183,16 +1182,16 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1696,13 +1695,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E69"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="5.08571428571429" style="2" customWidth="1"/>
-    <col min="2" max="2" width="29.4285714285714" customWidth="1"/>
-    <col min="3" max="3" width="33.4285714285714" customWidth="1"/>
-    <col min="4" max="4" width="17.8571428571429" customWidth="1"/>
-    <col min="5" max="5" width="46.1809523809524" customWidth="1"/>
+    <col min="1" max="1" width="5.0859375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="29.4296875" customWidth="1"/>
+    <col min="3" max="3" width="33.4296875" customWidth="1"/>
+    <col min="4" max="4" width="17.859375" customWidth="1"/>
+    <col min="5" max="5" width="46.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">

--- a/SUPPLIER RELATED/Phone Book BALAGAN.xlsx
+++ b/SUPPLIER RELATED/Phone Book BALAGAN.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17000"/>
+    <workbookView windowWidth="19635" windowHeight="7500"/>
   </bookViews>
   <sheets>
     <sheet name="Contact lists" sheetId="1" r:id="rId1"/>
@@ -152,7 +152,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="172">
   <si>
     <t>BALAGAN RESTO &amp; LOUNGE BAR</t>
   </si>
@@ -653,6 +653,21 @@
   </si>
   <si>
     <t>+62 877-2913-3528</t>
+  </si>
+  <si>
+    <t>Abiseka 2nd</t>
+  </si>
+  <si>
+    <t>Fresh milk</t>
+  </si>
+  <si>
+    <t>081703200100</t>
+  </si>
+  <si>
+    <t>Dairy fresh milk 1st</t>
+  </si>
+  <si>
+    <t>089529399287</t>
   </si>
 </sst>
 </file>
@@ -660,10 +675,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -832,12 +847,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="Times New Roman"/>
       <charset val="0"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="Times New Roman"/>
       <charset val="0"/>
@@ -1182,16 +1197,16 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1322,7 +1337,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1371,10 +1386,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1694,14 +1711,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E69"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="4"/>
+  <dimension ref="A1:E71"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="5.0859375" style="2" customWidth="1"/>
-    <col min="2" max="2" width="29.4296875" customWidth="1"/>
-    <col min="3" max="3" width="33.4296875" customWidth="1"/>
-    <col min="4" max="4" width="17.859375" customWidth="1"/>
-    <col min="5" max="5" width="46.1796875" customWidth="1"/>
+    <col min="1" max="1" width="5.08571428571429" style="2" customWidth="1"/>
+    <col min="2" max="2" width="29.4285714285714" customWidth="1"/>
+    <col min="3" max="3" width="33.4285714285714" customWidth="1"/>
+    <col min="4" max="4" width="17.8571428571429" customWidth="1"/>
+    <col min="5" max="5" width="46.1809523809524" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1807,7 +1824,7 @@
       <c r="C10" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="18" t="s">
+      <c r="D10" s="19" t="s">
         <v>18</v>
       </c>
       <c r="E10" s="10"/>
@@ -1870,7 +1887,7 @@
       <c r="C16" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="D16" s="18" t="s">
+      <c r="D16" s="19" t="s">
         <v>24</v>
       </c>
       <c r="E16" s="10" t="s">
@@ -1902,7 +1919,7 @@
       <c r="C18" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="D18" s="18" t="s">
+      <c r="D18" s="19" t="s">
         <v>31</v>
       </c>
       <c r="E18" s="10"/>
@@ -2117,7 +2134,7 @@
       <c r="C34" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="D34" s="19" t="s">
+      <c r="D34" s="20" t="s">
         <v>66</v>
       </c>
       <c r="E34" s="10" t="s">
@@ -2134,7 +2151,7 @@
       <c r="C35" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="D35" s="19" t="s">
+      <c r="D35" s="20" t="s">
         <v>70</v>
       </c>
       <c r="E35" s="10" t="s">
@@ -2151,7 +2168,7 @@
       <c r="C36" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="D36" s="19" t="s">
+      <c r="D36" s="20" t="s">
         <v>73</v>
       </c>
       <c r="E36" s="10" t="s">
@@ -2168,7 +2185,7 @@
       <c r="C37" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="D37" s="19" t="s">
+      <c r="D37" s="20" t="s">
         <v>76</v>
       </c>
       <c r="E37" s="10" t="s">
@@ -2185,7 +2202,7 @@
       <c r="C38" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="D38" s="19" t="s">
+      <c r="D38" s="20" t="s">
         <v>80</v>
       </c>
       <c r="E38" s="10"/>
@@ -2200,7 +2217,7 @@
       <c r="C39" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="D39" s="19" t="s">
+      <c r="D39" s="20" t="s">
         <v>83</v>
       </c>
       <c r="E39" s="10"/>
@@ -2249,7 +2266,7 @@
       <c r="C42" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="D42" s="19" t="s">
+      <c r="D42" s="20" t="s">
         <v>93</v>
       </c>
       <c r="E42" s="10" t="s">
@@ -2300,7 +2317,7 @@
       <c r="C45" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="D45" s="19" t="s">
+      <c r="D45" s="20" t="s">
         <v>101</v>
       </c>
       <c r="E45" s="10" t="s">
@@ -2317,7 +2334,7 @@
       <c r="C46" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="D46" s="19" t="s">
+      <c r="D46" s="20" t="s">
         <v>104</v>
       </c>
       <c r="E46" s="10"/>
@@ -2349,7 +2366,7 @@
       <c r="C48" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="D48" s="19" t="s">
+      <c r="D48" s="20" t="s">
         <v>110</v>
       </c>
       <c r="E48" s="10" t="s">
@@ -2366,7 +2383,7 @@
       <c r="C49" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="D49" s="19" t="s">
+      <c r="D49" s="20" t="s">
         <v>113</v>
       </c>
       <c r="E49" s="10" t="s">
@@ -2383,7 +2400,7 @@
       <c r="C50" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="D50" s="19" t="s">
+      <c r="D50" s="20" t="s">
         <v>116</v>
       </c>
       <c r="E50" s="10" t="s">
@@ -2477,7 +2494,7 @@
       <c r="C57" s="15" t="s">
         <v>129</v>
       </c>
-      <c r="D57" s="19" t="s">
+      <c r="D57" s="20" t="s">
         <v>130</v>
       </c>
       <c r="E57" s="10"/>
@@ -2493,7 +2510,7 @@
       <c r="C58" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="D58" s="19" t="s">
+      <c r="D58" s="20" t="s">
         <v>133</v>
       </c>
       <c r="E58" s="10"/>
@@ -2597,7 +2614,7 @@
       <c r="C64" s="15" t="s">
         <v>152</v>
       </c>
-      <c r="D64" s="19" t="s">
+      <c r="D64" s="20" t="s">
         <v>153</v>
       </c>
       <c r="E64" s="10"/>
@@ -2629,7 +2646,7 @@
       <c r="C66" s="15" t="s">
         <v>158</v>
       </c>
-      <c r="D66" s="19" t="s">
+      <c r="D66" s="20" t="s">
         <v>159</v>
       </c>
       <c r="E66" s="10"/>
@@ -2645,7 +2662,7 @@
       <c r="C67" s="15" t="s">
         <v>161</v>
       </c>
-      <c r="D67" s="19" t="s">
+      <c r="D67" s="20" t="s">
         <v>162</v>
       </c>
       <c r="E67" s="10"/>
@@ -2659,7 +2676,7 @@
         <v>163</v>
       </c>
       <c r="C68" s="15"/>
-      <c r="D68" s="19" t="s">
+      <c r="D68" s="20" t="s">
         <v>164</v>
       </c>
       <c r="E68" s="10"/>
@@ -2674,12 +2691,42 @@
       <c r="C69" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="D69" s="19" t="s">
+      <c r="D69" s="20" t="s">
         <v>166</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>147</v>
       </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="14">
+        <v>15</v>
+      </c>
+      <c r="B70" s="18" t="s">
+        <v>167</v>
+      </c>
+      <c r="C70" s="18" t="s">
+        <v>168</v>
+      </c>
+      <c r="D70" s="21" t="s">
+        <v>169</v>
+      </c>
+      <c r="E70" s="18"/>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="14">
+        <v>16</v>
+      </c>
+      <c r="B71" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="C71" s="18" t="s">
+        <v>168</v>
+      </c>
+      <c r="D71" s="21" t="s">
+        <v>171</v>
+      </c>
+      <c r="E71" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/SUPPLIER RELATED/Phone Book BALAGAN.xlsx
+++ b/SUPPLIER RELATED/Phone Book BALAGAN.xlsx
@@ -72,7 +72,8 @@
             <rFont val="Times New Roman"/>
             <charset val="0"/>
           </rPr>
-          <t>Cape discovery (wine)</t>
+          <t>Cape discovery (wine)
+Jim Beam</t>
         </r>
       </text>
     </comment>
@@ -152,7 +153,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="173">
   <si>
     <t>BALAGAN RESTO &amp; LOUNGE BAR</t>
   </si>
@@ -521,6 +522,9 @@
   </si>
   <si>
     <t>0813-3847-4143</t>
+  </si>
+  <si>
+    <t>Nano Dewata</t>
   </si>
   <si>
     <t>KITCHEN</t>
@@ -847,12 +851,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="Times New Roman"/>
       <charset val="0"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="Times New Roman"/>
       <charset val="0"/>
@@ -1337,7 +1341,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1386,12 +1390,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1711,7 +1713,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E71"/>
+  <dimension ref="A1:E72"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="5.08571428571429" style="2" customWidth="1"/>
@@ -1824,7 +1826,7 @@
       <c r="C10" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="19" t="s">
+      <c r="D10" s="18" t="s">
         <v>18</v>
       </c>
       <c r="E10" s="10"/>
@@ -1887,7 +1889,7 @@
       <c r="C16" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="D16" s="19" t="s">
+      <c r="D16" s="18" t="s">
         <v>24</v>
       </c>
       <c r="E16" s="10" t="s">
@@ -1919,7 +1921,7 @@
       <c r="C18" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="D18" s="19" t="s">
+      <c r="D18" s="18" t="s">
         <v>31</v>
       </c>
       <c r="E18" s="10"/>
@@ -2134,7 +2136,7 @@
       <c r="C34" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="D34" s="20" t="s">
+      <c r="D34" s="19" t="s">
         <v>66</v>
       </c>
       <c r="E34" s="10" t="s">
@@ -2151,7 +2153,7 @@
       <c r="C35" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="D35" s="20" t="s">
+      <c r="D35" s="19" t="s">
         <v>70</v>
       </c>
       <c r="E35" s="10" t="s">
@@ -2168,7 +2170,7 @@
       <c r="C36" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="D36" s="20" t="s">
+      <c r="D36" s="19" t="s">
         <v>73</v>
       </c>
       <c r="E36" s="10" t="s">
@@ -2185,7 +2187,7 @@
       <c r="C37" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="D37" s="20" t="s">
+      <c r="D37" s="19" t="s">
         <v>76</v>
       </c>
       <c r="E37" s="10" t="s">
@@ -2202,7 +2204,7 @@
       <c r="C38" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="D38" s="20" t="s">
+      <c r="D38" s="19" t="s">
         <v>80</v>
       </c>
       <c r="E38" s="10"/>
@@ -2217,7 +2219,7 @@
       <c r="C39" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="D39" s="20" t="s">
+      <c r="D39" s="19" t="s">
         <v>83</v>
       </c>
       <c r="E39" s="10"/>
@@ -2266,7 +2268,7 @@
       <c r="C42" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="D42" s="20" t="s">
+      <c r="D42" s="19" t="s">
         <v>93</v>
       </c>
       <c r="E42" s="10" t="s">
@@ -2317,7 +2319,7 @@
       <c r="C45" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="D45" s="20" t="s">
+      <c r="D45" s="19" t="s">
         <v>101</v>
       </c>
       <c r="E45" s="10" t="s">
@@ -2334,7 +2336,7 @@
       <c r="C46" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="D46" s="20" t="s">
+      <c r="D46" s="19" t="s">
         <v>104</v>
       </c>
       <c r="E46" s="10"/>
@@ -2366,7 +2368,7 @@
       <c r="C48" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="D48" s="20" t="s">
+      <c r="D48" s="19" t="s">
         <v>110</v>
       </c>
       <c r="E48" s="10" t="s">
@@ -2383,7 +2385,7 @@
       <c r="C49" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="D49" s="20" t="s">
+      <c r="D49" s="19" t="s">
         <v>113</v>
       </c>
       <c r="E49" s="10" t="s">
@@ -2400,7 +2402,7 @@
       <c r="C50" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="D50" s="20" t="s">
+      <c r="D50" s="19" t="s">
         <v>116</v>
       </c>
       <c r="E50" s="10" t="s">
@@ -2437,302 +2439,312 @@
       </c>
       <c r="E52" s="10"/>
     </row>
-    <row r="53" spans="2:4">
-      <c r="B53" s="17"/>
+    <row r="53" spans="1:4">
+      <c r="A53" s="2">
+        <v>22</v>
+      </c>
+      <c r="B53" s="17" t="s">
+        <v>123</v>
+      </c>
       <c r="C53" s="17"/>
       <c r="D53" s="17"/>
     </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="11" t="s">
-        <v>123</v>
-      </c>
-      <c r="B54" s="11"/>
-      <c r="C54" s="11"/>
-      <c r="D54" s="11"/>
-      <c r="E54" s="11"/>
+    <row r="54" spans="2:4">
+      <c r="B54" s="17"/>
+      <c r="C54" s="17"/>
+      <c r="D54" s="17"/>
     </row>
     <row r="55" spans="1:5">
-      <c r="A55" s="12" t="s">
+      <c r="A55" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="B55" s="11"/>
+      <c r="C55" s="11"/>
+      <c r="D55" s="11"/>
+      <c r="E55" s="11"/>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="B55" s="13" t="s">
+      <c r="B56" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="C55" s="13"/>
-      <c r="D55" s="13" t="s">
+      <c r="C56" s="13"/>
+      <c r="D56" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="E55" s="13" t="s">
+      <c r="E56" s="13" t="s">
         <v>8</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="14">
-        <v>1</v>
-      </c>
-      <c r="B56" s="15" t="s">
-        <v>124</v>
-      </c>
-      <c r="C56" s="15" t="s">
-        <v>125</v>
-      </c>
-      <c r="D56" s="15" t="s">
-        <v>126</v>
-      </c>
-      <c r="E56" s="10" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="14">
-        <f t="shared" ref="A57:A68" si="0">A56+1</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B57" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="C57" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="D57" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="E57" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="C57" s="15" t="s">
-        <v>129</v>
-      </c>
-      <c r="D57" s="20" t="s">
-        <v>130</v>
-      </c>
-      <c r="E57" s="10"/>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="14">
-        <f t="shared" si="0"/>
-        <v>3</v>
+        <f t="shared" ref="A58:A69" si="0">A57+1</f>
+        <v>2</v>
       </c>
       <c r="B58" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="C58" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="D58" s="19" t="s">
         <v>131</v>
-      </c>
-      <c r="C58" s="15" t="s">
-        <v>132</v>
-      </c>
-      <c r="D58" s="20" t="s">
-        <v>133</v>
       </c>
       <c r="E58" s="10"/>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="14">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B59" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="C59" s="15" t="s">
+        <v>133</v>
+      </c>
+      <c r="D59" s="19" t="s">
         <v>134</v>
       </c>
-      <c r="C59" s="15" t="s">
-        <v>135</v>
-      </c>
-      <c r="D59" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="E59" s="10" t="s">
-        <v>10</v>
-      </c>
+      <c r="E59" s="10"/>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="14">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B60" s="15" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C60" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="D60" s="15" t="s">
         <v>137</v>
       </c>
-      <c r="D60" s="15" t="s">
-        <v>138</v>
-      </c>
       <c r="E60" s="10" t="s">
-        <v>139</v>
+        <v>10</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="14">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B61" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="C61" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="D61" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="E61" s="10" t="s">
         <v>140</v>
-      </c>
-      <c r="C61" s="15" t="s">
-        <v>141</v>
-      </c>
-      <c r="D61" s="15" t="s">
-        <v>142</v>
-      </c>
-      <c r="E61" s="10" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="14">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B62" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="C62" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="D62" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="E62" s="10" t="s">
         <v>144</v>
-      </c>
-      <c r="C62" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="D62" s="15" t="s">
-        <v>146</v>
-      </c>
-      <c r="E62" s="10" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="14">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B63" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="C63" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="D63" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="E63" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="C63" s="15" t="s">
-        <v>149</v>
-      </c>
-      <c r="D63" s="15" t="s">
-        <v>150</v>
-      </c>
-      <c r="E63" s="10"/>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="14">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B64" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="C64" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="D64" s="15" t="s">
         <v>151</v>
-      </c>
-      <c r="C64" s="15" t="s">
-        <v>152</v>
-      </c>
-      <c r="D64" s="20" t="s">
-        <v>153</v>
       </c>
       <c r="E64" s="10"/>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="14">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B65" s="15" t="s">
+        <v>152</v>
+      </c>
+      <c r="C65" s="15" t="s">
+        <v>153</v>
+      </c>
+      <c r="D65" s="19" t="s">
         <v>154</v>
-      </c>
-      <c r="C65" s="15" t="s">
-        <v>155</v>
-      </c>
-      <c r="D65" s="15" t="s">
-        <v>156</v>
       </c>
       <c r="E65" s="10"/>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="14">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B66" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="C66" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="D66" s="15" t="s">
         <v>157</v>
-      </c>
-      <c r="C66" s="15" t="s">
-        <v>158</v>
-      </c>
-      <c r="D66" s="20" t="s">
-        <v>159</v>
       </c>
       <c r="E66" s="10"/>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="14">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B67" s="15" t="s">
+        <v>158</v>
+      </c>
+      <c r="C67" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="D67" s="19" t="s">
         <v>160</v>
-      </c>
-      <c r="C67" s="15" t="s">
-        <v>161</v>
-      </c>
-      <c r="D67" s="20" t="s">
-        <v>162</v>
       </c>
       <c r="E67" s="10"/>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="14">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B68" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="C68" s="15" t="s">
+        <v>162</v>
+      </c>
+      <c r="D68" s="19" t="s">
         <v>163</v>
-      </c>
-      <c r="C68" s="15"/>
-      <c r="D68" s="20" t="s">
-        <v>164</v>
       </c>
       <c r="E68" s="10"/>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="14">
-        <v>14</v>
-      </c>
-      <c r="B69" s="10" t="s">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="B69" s="15" t="s">
+        <v>164</v>
+      </c>
+      <c r="C69" s="15"/>
+      <c r="D69" s="19" t="s">
         <v>165</v>
       </c>
-      <c r="C69" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="D69" s="20" t="s">
-        <v>166</v>
-      </c>
-      <c r="E69" s="10" t="s">
-        <v>147</v>
-      </c>
+      <c r="E69" s="10"/>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="14">
-        <v>15</v>
-      </c>
-      <c r="B70" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="B70" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="C70" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="D70" s="19" t="s">
         <v>167</v>
       </c>
-      <c r="C70" s="18" t="s">
-        <v>168</v>
-      </c>
-      <c r="D70" s="21" t="s">
-        <v>169</v>
-      </c>
-      <c r="E70" s="18"/>
+      <c r="E70" s="10" t="s">
+        <v>148</v>
+      </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="14">
+        <v>15</v>
+      </c>
+      <c r="B71" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="C71" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="D71" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="E71" s="10"/>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="14">
         <v>16</v>
       </c>
-      <c r="B71" s="18" t="s">
-        <v>170</v>
-      </c>
-      <c r="C71" s="18" t="s">
-        <v>168</v>
-      </c>
-      <c r="D71" s="21" t="s">
+      <c r="B72" s="10" t="s">
         <v>171</v>
       </c>
-      <c r="E71" s="18"/>
+      <c r="C72" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="D72" s="18" t="s">
+        <v>172</v>
+      </c>
+      <c r="E72" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A14:E14"/>
     <mergeCell ref="A32:E32"/>
-    <mergeCell ref="A54:E54"/>
+    <mergeCell ref="A55:E55"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A4" r:id="rId3" display="balagan.uluwatu@gmail.com"/>

--- a/SUPPLIER RELATED/Phone Book BALAGAN.xlsx
+++ b/SUPPLIER RELATED/Phone Book BALAGAN.xlsx
@@ -153,7 +153,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="176">
   <si>
     <t>BALAGAN RESTO &amp; LOUNGE BAR</t>
   </si>
@@ -525,6 +525,15 @@
   </si>
   <si>
     <t>Nano Dewata</t>
+  </si>
+  <si>
+    <t>Dineta Jaya</t>
+  </si>
+  <si>
+    <t>Oil, French fries, frozen, Olive Oil, Dairy (Yoghurt)</t>
+  </si>
+  <si>
+    <t>0878-6021-7745</t>
   </si>
   <si>
     <t>KITCHEN</t>
@@ -851,12 +860,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="Times New Roman"/>
       <charset val="0"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="Times New Roman"/>
       <charset val="0"/>
@@ -1387,8 +1396,8 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
@@ -1713,7 +1722,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E72"/>
+  <dimension ref="A1:E73"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="5.08571428571429" style="2" customWidth="1"/>
@@ -2439,82 +2448,84 @@
       </c>
       <c r="E52" s="10"/>
     </row>
-    <row r="53" spans="1:4">
-      <c r="A53" s="2">
+    <row r="53" spans="1:5">
+      <c r="A53" s="14">
         <v>22</v>
       </c>
-      <c r="B53" s="17" t="s">
+      <c r="B53" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="C53" s="17"/>
-      <c r="D53" s="17"/>
-    </row>
-    <row r="54" spans="2:4">
-      <c r="B54" s="17"/>
-      <c r="C54" s="17"/>
-      <c r="D54" s="17"/>
+      <c r="C53" s="15"/>
+      <c r="D53" s="15"/>
+      <c r="E53" s="10"/>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="14">
+        <v>23</v>
+      </c>
+      <c r="B54" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="C54" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="D54" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="E54" s="10"/>
     </row>
     <row r="55" spans="1:5">
-      <c r="A55" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="B55" s="11"/>
-      <c r="C55" s="11"/>
-      <c r="D55" s="11"/>
-      <c r="E55" s="11"/>
+      <c r="A55" s="17"/>
+      <c r="B55" s="17"/>
+      <c r="C55" s="17"/>
+      <c r="D55" s="17"/>
+      <c r="E55" s="17"/>
     </row>
     <row r="56" spans="1:5">
-      <c r="A56" s="12" t="s">
+      <c r="A56" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B56" s="11"/>
+      <c r="C56" s="11"/>
+      <c r="D56" s="11"/>
+      <c r="E56" s="11"/>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="B56" s="13" t="s">
+      <c r="B57" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="C56" s="13"/>
-      <c r="D56" s="13" t="s">
+      <c r="C57" s="13"/>
+      <c r="D57" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="E56" s="13" t="s">
+      <c r="E57" s="13" t="s">
         <v>8</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="14">
-        <v>1</v>
-      </c>
-      <c r="B57" s="15" t="s">
-        <v>125</v>
-      </c>
-      <c r="C57" s="15" t="s">
-        <v>126</v>
-      </c>
-      <c r="D57" s="15" t="s">
-        <v>127</v>
-      </c>
-      <c r="E57" s="10" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="14">
-        <f t="shared" ref="A58:A69" si="0">A57+1</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B58" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="C58" s="15" t="s">
         <v>129</v>
       </c>
-      <c r="C58" s="15" t="s">
+      <c r="D58" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="D58" s="19" t="s">
+      <c r="E58" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="E58" s="10"/>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="14">
-        <f t="shared" si="0"/>
-        <v>3</v>
+        <f t="shared" ref="A59:A70" si="0">A58+1</f>
+        <v>2</v>
       </c>
       <c r="B59" s="15" t="s">
         <v>132</v>
@@ -2530,7 +2541,7 @@
     <row r="60" spans="1:5">
       <c r="A60" s="14">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B60" s="15" t="s">
         <v>135</v>
@@ -2538,87 +2549,87 @@
       <c r="C60" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="D60" s="15" t="s">
+      <c r="D60" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="E60" s="10" t="s">
-        <v>10</v>
-      </c>
+      <c r="E60" s="10"/>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="14">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B61" s="15" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C61" s="15" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D61" s="15" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>140</v>
+        <v>10</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="14">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B62" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="C62" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="C62" s="15" t="s">
+      <c r="D62" s="15" t="s">
         <v>142</v>
       </c>
-      <c r="D62" s="15" t="s">
+      <c r="E62" s="10" t="s">
         <v>143</v>
-      </c>
-      <c r="E62" s="10" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="14">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B63" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="C63" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="C63" s="15" t="s">
+      <c r="D63" s="15" t="s">
         <v>146</v>
       </c>
-      <c r="D63" s="15" t="s">
+      <c r="E63" s="10" t="s">
         <v>147</v>
-      </c>
-      <c r="E63" s="10" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="14">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B64" s="15" t="s">
+        <v>148</v>
+      </c>
+      <c r="C64" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="C64" s="15" t="s">
+      <c r="D64" s="15" t="s">
         <v>150</v>
       </c>
-      <c r="D64" s="15" t="s">
+      <c r="E64" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="E64" s="10"/>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="14">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B65" s="15" t="s">
         <v>152</v>
@@ -2626,7 +2637,7 @@
       <c r="C65" s="15" t="s">
         <v>153</v>
       </c>
-      <c r="D65" s="19" t="s">
+      <c r="D65" s="15" t="s">
         <v>154</v>
       </c>
       <c r="E65" s="10"/>
@@ -2634,7 +2645,7 @@
     <row r="66" spans="1:5">
       <c r="A66" s="14">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B66" s="15" t="s">
         <v>155</v>
@@ -2642,7 +2653,7 @@
       <c r="C66" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="D66" s="15" t="s">
+      <c r="D66" s="19" t="s">
         <v>157</v>
       </c>
       <c r="E66" s="10"/>
@@ -2650,7 +2661,7 @@
     <row r="67" spans="1:5">
       <c r="A67" s="14">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B67" s="15" t="s">
         <v>158</v>
@@ -2658,7 +2669,7 @@
       <c r="C67" s="15" t="s">
         <v>159</v>
       </c>
-      <c r="D67" s="19" t="s">
+      <c r="D67" s="15" t="s">
         <v>160</v>
       </c>
       <c r="E67" s="10"/>
@@ -2666,7 +2677,7 @@
     <row r="68" spans="1:5">
       <c r="A68" s="14">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B68" s="15" t="s">
         <v>161</v>
@@ -2682,69 +2693,85 @@
     <row r="69" spans="1:5">
       <c r="A69" s="14">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B69" s="15" t="s">
         <v>164</v>
       </c>
-      <c r="C69" s="15"/>
+      <c r="C69" s="15" t="s">
+        <v>165</v>
+      </c>
       <c r="D69" s="19" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E69" s="10"/>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="14">
-        <v>14</v>
-      </c>
-      <c r="B70" s="10" t="s">
-        <v>166</v>
-      </c>
-      <c r="C70" s="10" t="s">
-        <v>162</v>
-      </c>
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="B70" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="C70" s="15"/>
       <c r="D70" s="19" t="s">
-        <v>167</v>
-      </c>
-      <c r="E70" s="10" t="s">
-        <v>148</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="E70" s="10"/>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="14">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B71" s="10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C71" s="10" t="s">
-        <v>169</v>
-      </c>
-      <c r="D71" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="D71" s="19" t="s">
         <v>170</v>
       </c>
-      <c r="E71" s="10"/>
+      <c r="E71" s="10" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="14">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B72" s="10" t="s">
         <v>171</v>
       </c>
       <c r="C72" s="10" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="D72" s="18" t="s">
+        <v>173</v>
+      </c>
+      <c r="E72" s="10"/>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="14">
+        <v>16</v>
+      </c>
+      <c r="B73" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="C73" s="10" t="s">
         <v>172</v>
       </c>
-      <c r="E72" s="10"/>
+      <c r="D73" s="18" t="s">
+        <v>175</v>
+      </c>
+      <c r="E73" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A14:E14"/>
     <mergeCell ref="A32:E32"/>
-    <mergeCell ref="A55:E55"/>
+    <mergeCell ref="A56:E56"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A4" r:id="rId3" display="balagan.uluwatu@gmail.com"/>

--- a/SUPPLIER RELATED/Phone Book BALAGAN.xlsx
+++ b/SUPPLIER RELATED/Phone Book BALAGAN.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19635" windowHeight="7500"/>
+    <workbookView windowHeight="16040"/>
   </bookViews>
   <sheets>
     <sheet name="Contact lists" sheetId="1" r:id="rId1"/>
@@ -688,10 +688,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -860,12 +860,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="Times New Roman"/>
       <charset val="0"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="Times New Roman"/>
       <charset val="0"/>
@@ -1210,16 +1210,16 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1723,13 +1723,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E73"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="5.08571428571429" style="2" customWidth="1"/>
-    <col min="2" max="2" width="29.4285714285714" customWidth="1"/>
-    <col min="3" max="3" width="33.4285714285714" customWidth="1"/>
-    <col min="4" max="4" width="17.8571428571429" customWidth="1"/>
-    <col min="5" max="5" width="46.1809523809524" customWidth="1"/>
+    <col min="1" max="1" width="5.0859375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="29.4296875" customWidth="1"/>
+    <col min="3" max="3" width="33.4296875" customWidth="1"/>
+    <col min="4" max="4" width="17.859375" customWidth="1"/>
+    <col min="5" max="5" width="46.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">

--- a/SUPPLIER RELATED/Phone Book BALAGAN.xlsx
+++ b/SUPPLIER RELATED/Phone Book BALAGAN.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16040"/>
+    <workbookView windowHeight="17020"/>
   </bookViews>
   <sheets>
     <sheet name="Contact lists" sheetId="1" r:id="rId1"/>
@@ -153,7 +153,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="179">
   <si>
     <t>BALAGAN RESTO &amp; LOUNGE BAR</t>
   </si>
@@ -527,160 +527,169 @@
     <t>Nano Dewata</t>
   </si>
   <si>
+    <t>Indobev Mentari Sejahtera</t>
+  </si>
+  <si>
+    <t>Bols triple sec</t>
+  </si>
+  <si>
+    <t>+62 821-4627-8921</t>
+  </si>
+  <si>
+    <t>KITCHEN</t>
+  </si>
+  <si>
+    <t>Bu Bunga</t>
+  </si>
+  <si>
+    <t>Groceries</t>
+  </si>
+  <si>
+    <t>+62 881-0370-16365</t>
+  </si>
+  <si>
+    <t>Nias</t>
+  </si>
+  <si>
+    <t>Aroma</t>
+  </si>
+  <si>
+    <t>Bf Sausage &amp; Bacon</t>
+  </si>
+  <si>
+    <t>0896-7013-7841</t>
+  </si>
+  <si>
+    <t>Krop Nation</t>
+  </si>
+  <si>
+    <t>Flower for Food</t>
+  </si>
+  <si>
+    <t>0856-3761-890</t>
+  </si>
+  <si>
+    <t>Rafi Seafood</t>
+  </si>
+  <si>
+    <t>Seafood</t>
+  </si>
+  <si>
+    <t>+62 822-6661-9799</t>
+  </si>
+  <si>
+    <t>Admin Rafi</t>
+  </si>
+  <si>
+    <t>+62 823-3903-0247</t>
+  </si>
+  <si>
+    <t>Admin</t>
+  </si>
+  <si>
+    <t>Kusuma Surya Pangan</t>
+  </si>
+  <si>
+    <t>Chicken</t>
+  </si>
+  <si>
+    <t>+62 812-1744-8920</t>
+  </si>
+  <si>
+    <t>Sales KSP</t>
+  </si>
+  <si>
+    <t>Surya Cipta Niaga</t>
+  </si>
+  <si>
+    <t>Beef Meat</t>
+  </si>
+  <si>
+    <t>+62 851-0051-9824</t>
+  </si>
+  <si>
+    <t>to ask for outstandings / week</t>
+  </si>
+  <si>
+    <t>Bayu Agni Merta</t>
+  </si>
+  <si>
+    <t>Gas</t>
+  </si>
+  <si>
+    <t>+62 822-3748-2976</t>
+  </si>
+  <si>
+    <t>Joy Green</t>
+  </si>
+  <si>
+    <t>Mix Berry</t>
+  </si>
+  <si>
+    <t>+62 822-3483-2075</t>
+  </si>
+  <si>
+    <t>Celebrity Bakery</t>
+  </si>
+  <si>
+    <t>Bakery</t>
+  </si>
+  <si>
+    <t>+62 851-0098-5124</t>
+  </si>
+  <si>
+    <t>Surbled Meat</t>
+  </si>
+  <si>
+    <t>Tuna, Mahi", Salmon, Chicken</t>
+  </si>
+  <si>
+    <t>0813-7024-7555</t>
+  </si>
+  <si>
+    <t>Mama Rada Admin</t>
+  </si>
+  <si>
+    <t>Dumpling &amp; Syrniki</t>
+  </si>
+  <si>
+    <t>0823-3479-7848</t>
+  </si>
+  <si>
+    <t>UD Putra (Pak Wahyu)</t>
+  </si>
+  <si>
+    <t>0823-4087-4469</t>
+  </si>
+  <si>
+    <t>Boiler</t>
+  </si>
+  <si>
+    <t>+62 877-2913-3528</t>
+  </si>
+  <si>
+    <t>Abiseka 2nd</t>
+  </si>
+  <si>
+    <t>Fresh milk</t>
+  </si>
+  <si>
+    <t>081703200100</t>
+  </si>
+  <si>
+    <t>Dairy fresh milk 1st</t>
+  </si>
+  <si>
+    <t>089529399287</t>
+  </si>
+  <si>
     <t>Dineta Jaya</t>
   </si>
   <si>
     <t>Oil, French fries, frozen, Olive Oil, Dairy (Yoghurt)</t>
   </si>
   <si>
-    <t>0878-6021-7745</t>
-  </si>
-  <si>
-    <t>KITCHEN</t>
-  </si>
-  <si>
-    <t>Bu Bunga</t>
-  </si>
-  <si>
-    <t>Groceries</t>
-  </si>
-  <si>
-    <t>+62 881-0370-16365</t>
-  </si>
-  <si>
-    <t>Nias</t>
-  </si>
-  <si>
-    <t>Aroma</t>
-  </si>
-  <si>
-    <t>Bf Sausage &amp; Bacon</t>
-  </si>
-  <si>
-    <t>0896-7013-7841</t>
-  </si>
-  <si>
-    <t>Krop Nation</t>
-  </si>
-  <si>
-    <t>Flower for Food</t>
-  </si>
-  <si>
-    <t>0856-3761-890</t>
-  </si>
-  <si>
-    <t>Rafi Seafood</t>
-  </si>
-  <si>
-    <t>Seafood</t>
-  </si>
-  <si>
-    <t>+62 822-6661-9799</t>
-  </si>
-  <si>
-    <t>Admin Rafi</t>
-  </si>
-  <si>
-    <t>+62 823-3903-0247</t>
-  </si>
-  <si>
-    <t>Admin</t>
-  </si>
-  <si>
-    <t>Kusuma Surya Pangan</t>
-  </si>
-  <si>
-    <t>Chicken</t>
-  </si>
-  <si>
-    <t>+62 812-1744-8920</t>
-  </si>
-  <si>
-    <t>Sales KSP</t>
-  </si>
-  <si>
-    <t>Surya Cipta Niaga</t>
-  </si>
-  <si>
-    <t>Beef Meat</t>
-  </si>
-  <si>
-    <t>+62 851-0051-9824</t>
-  </si>
-  <si>
-    <t>to ask for outstandings / week</t>
-  </si>
-  <si>
-    <t>Bayu Agni Merta</t>
-  </si>
-  <si>
-    <t>Gas</t>
-  </si>
-  <si>
-    <t>+62 822-3748-2976</t>
-  </si>
-  <si>
-    <t>Joy Green</t>
-  </si>
-  <si>
-    <t>Mix Berry</t>
-  </si>
-  <si>
-    <t>+62 822-3483-2075</t>
-  </si>
-  <si>
-    <t>Celebrity Bakery</t>
-  </si>
-  <si>
-    <t>Bakery</t>
-  </si>
-  <si>
-    <t>+62 851-0098-5124</t>
-  </si>
-  <si>
-    <t>Surbled Meat</t>
-  </si>
-  <si>
-    <t>Tuna, Mahi", Salmon, Chicken</t>
-  </si>
-  <si>
-    <t>0813-7024-7555</t>
-  </si>
-  <si>
-    <t>Mama Rada Admin</t>
-  </si>
-  <si>
-    <t>Dumpling &amp; Syrniki</t>
-  </si>
-  <si>
-    <t>0823-3479-7848</t>
-  </si>
-  <si>
-    <t>UD Putra (Pak Wahyu)</t>
-  </si>
-  <si>
-    <t>0823-4087-4469</t>
-  </si>
-  <si>
-    <t>Boiler</t>
-  </si>
-  <si>
-    <t>+62 877-2913-3528</t>
-  </si>
-  <si>
-    <t>Abiseka 2nd</t>
-  </si>
-  <si>
-    <t>Fresh milk</t>
-  </si>
-  <si>
-    <t>081703200100</t>
-  </si>
-  <si>
-    <t>Dairy fresh milk 1st</t>
-  </si>
-  <si>
-    <t>089529399287</t>
+    <t>0878-6021-7746</t>
   </si>
 </sst>
 </file>
@@ -1722,7 +1731,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E73"/>
+  <dimension ref="A1:E75"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="5.0859375" style="2" customWidth="1"/>
@@ -2469,309 +2478,324 @@
       <c r="C54" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="D54" s="19" t="s">
+      <c r="D54" s="15" t="s">
         <v>126</v>
       </c>
       <c r="E54" s="10"/>
     </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="17"/>
-      <c r="B55" s="17"/>
-      <c r="C55" s="17"/>
-      <c r="D55" s="17"/>
-      <c r="E55" s="17"/>
-    </row>
     <row r="56" spans="1:5">
-      <c r="A56" s="11" t="s">
+      <c r="A56" s="17"/>
+      <c r="B56" s="17"/>
+      <c r="C56" s="17"/>
+      <c r="D56" s="17"/>
+      <c r="E56" s="17"/>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="B56" s="11"/>
-      <c r="C56" s="11"/>
-      <c r="D56" s="11"/>
-      <c r="E56" s="11"/>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="12" t="s">
+      <c r="B57" s="11"/>
+      <c r="C57" s="11"/>
+      <c r="D57" s="11"/>
+      <c r="E57" s="11"/>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="B57" s="13" t="s">
+      <c r="B58" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="C57" s="13"/>
-      <c r="D57" s="13" t="s">
+      <c r="C58" s="13"/>
+      <c r="D58" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="E57" s="13" t="s">
+      <c r="E58" s="13" t="s">
         <v>8</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="14">
-        <v>1</v>
-      </c>
-      <c r="B58" s="15" t="s">
-        <v>128</v>
-      </c>
-      <c r="C58" s="15" t="s">
-        <v>129</v>
-      </c>
-      <c r="D58" s="15" t="s">
-        <v>130</v>
-      </c>
-      <c r="E58" s="10" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="14">
-        <f t="shared" ref="A59:A70" si="0">A58+1</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B59" s="15" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C59" s="15" t="s">
-        <v>133</v>
-      </c>
-      <c r="D59" s="19" t="s">
-        <v>134</v>
-      </c>
-      <c r="E59" s="10"/>
+        <v>129</v>
+      </c>
+      <c r="D59" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="E59" s="10" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="14">
-        <f t="shared" si="0"/>
-        <v>3</v>
+        <f t="shared" ref="A60:A71" si="0">A59+1</f>
+        <v>2</v>
       </c>
       <c r="B60" s="15" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C60" s="15" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D60" s="19" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E60" s="10"/>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="14">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B61" s="15" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C61" s="15" t="s">
-        <v>139</v>
-      </c>
-      <c r="D61" s="15" t="s">
-        <v>140</v>
-      </c>
-      <c r="E61" s="10" t="s">
-        <v>10</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="D61" s="19" t="s">
+        <v>137</v>
+      </c>
+      <c r="E61" s="10"/>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="14">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B62" s="15" t="s">
         <v>138</v>
       </c>
       <c r="C62" s="15" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D62" s="15" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E62" s="10" t="s">
-        <v>143</v>
+        <v>10</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="14">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B63" s="15" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="C63" s="15" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="D63" s="15" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="14">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B64" s="15" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C64" s="15" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D64" s="15" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="E64" s="10" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="14">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B65" s="15" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C65" s="15" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="D65" s="15" t="s">
-        <v>154</v>
-      </c>
-      <c r="E65" s="10"/>
+        <v>150</v>
+      </c>
+      <c r="E65" s="10" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="14">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B66" s="15" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C66" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="D66" s="19" t="s">
-        <v>157</v>
+        <v>153</v>
+      </c>
+      <c r="D66" s="15" t="s">
+        <v>154</v>
       </c>
       <c r="E66" s="10"/>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="14">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B67" s="15" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C67" s="15" t="s">
-        <v>159</v>
-      </c>
-      <c r="D67" s="15" t="s">
-        <v>160</v>
+        <v>156</v>
+      </c>
+      <c r="D67" s="19" t="s">
+        <v>157</v>
       </c>
       <c r="E67" s="10"/>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="14">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B68" s="15" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C68" s="15" t="s">
-        <v>162</v>
-      </c>
-      <c r="D68" s="19" t="s">
-        <v>163</v>
+        <v>159</v>
+      </c>
+      <c r="D68" s="15" t="s">
+        <v>160</v>
       </c>
       <c r="E68" s="10"/>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="14">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B69" s="15" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C69" s="15" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D69" s="19" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="E69" s="10"/>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="14">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B70" s="15" t="s">
-        <v>167</v>
-      </c>
-      <c r="C70" s="15"/>
+        <v>164</v>
+      </c>
+      <c r="C70" s="15" t="s">
+        <v>165</v>
+      </c>
       <c r="D70" s="19" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E70" s="10"/>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="14">
-        <v>14</v>
-      </c>
-      <c r="B71" s="10" t="s">
-        <v>169</v>
-      </c>
-      <c r="C71" s="10" t="s">
-        <v>165</v>
-      </c>
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="B71" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="C71" s="15"/>
       <c r="D71" s="19" t="s">
-        <v>170</v>
-      </c>
-      <c r="E71" s="10" t="s">
-        <v>151</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="E71" s="10"/>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="14">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B72" s="10" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C72" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="D72" s="18" t="s">
-        <v>173</v>
-      </c>
-      <c r="E72" s="10"/>
+        <v>165</v>
+      </c>
+      <c r="D72" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="E72" s="10" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="14">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B73" s="10" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C73" s="10" t="s">
         <v>172</v>
       </c>
       <c r="D73" s="18" t="s">
+        <v>173</v>
+      </c>
+      <c r="E73" s="10"/>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="14">
+        <v>16</v>
+      </c>
+      <c r="B74" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="C74" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="D74" s="18" t="s">
         <v>175</v>
       </c>
-      <c r="E73" s="10"/>
+      <c r="E74" s="10"/>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="14">
+        <v>17</v>
+      </c>
+      <c r="B75" s="15" t="s">
+        <v>176</v>
+      </c>
+      <c r="C75" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="D75" s="19" t="s">
+        <v>178</v>
+      </c>
+      <c r="E75" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A14:E14"/>
     <mergeCell ref="A32:E32"/>
-    <mergeCell ref="A56:E56"/>
+    <mergeCell ref="A57:E57"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A4" r:id="rId3" display="balagan.uluwatu@gmail.com"/>

--- a/SUPPLIER RELATED/Phone Book BALAGAN.xlsx
+++ b/SUPPLIER RELATED/Phone Book BALAGAN.xlsx
@@ -153,7 +153,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="180">
   <si>
     <t>BALAGAN RESTO &amp; LOUNGE BAR</t>
   </si>
@@ -525,6 +525,9 @@
   </si>
   <si>
     <t>Nano Dewata</t>
+  </si>
+  <si>
+    <t>+62 878-1114-7765</t>
   </si>
   <si>
     <t>Indobev Mentari Sejahtera</t>
@@ -2465,7 +2468,9 @@
         <v>123</v>
       </c>
       <c r="C53" s="15"/>
-      <c r="D53" s="15"/>
+      <c r="D53" s="15" t="s">
+        <v>124</v>
+      </c>
       <c r="E53" s="10"/>
     </row>
     <row r="54" spans="1:5">
@@ -2473,13 +2478,13 @@
         <v>23</v>
       </c>
       <c r="B54" s="15" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C54" s="15" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D54" s="15" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E54" s="10"/>
     </row>
@@ -2492,7 +2497,7 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="11" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B57" s="11"/>
       <c r="C57" s="11"/>
@@ -2519,16 +2524,16 @@
         <v>1</v>
       </c>
       <c r="B59" s="15" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C59" s="15" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D59" s="15" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -2537,13 +2542,13 @@
         <v>2</v>
       </c>
       <c r="B60" s="15" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C60" s="15" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D60" s="19" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E60" s="10"/>
     </row>
@@ -2553,13 +2558,13 @@
         <v>3</v>
       </c>
       <c r="B61" s="15" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C61" s="15" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D61" s="19" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E61" s="10"/>
     </row>
@@ -2569,13 +2574,13 @@
         <v>4</v>
       </c>
       <c r="B62" s="15" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C62" s="15" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D62" s="15" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E62" s="10" t="s">
         <v>10</v>
@@ -2587,16 +2592,16 @@
         <v>5</v>
       </c>
       <c r="B63" s="15" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C63" s="15" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D63" s="15" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -2605,16 +2610,16 @@
         <v>6</v>
       </c>
       <c r="B64" s="15" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C64" s="15" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D64" s="15" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E64" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -2623,16 +2628,16 @@
         <v>7</v>
       </c>
       <c r="B65" s="15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C65" s="15" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D65" s="15" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -2641,13 +2646,13 @@
         <v>8</v>
       </c>
       <c r="B66" s="15" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C66" s="15" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D66" s="15" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E66" s="10"/>
     </row>
@@ -2657,13 +2662,13 @@
         <v>9</v>
       </c>
       <c r="B67" s="15" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C67" s="15" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D67" s="19" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E67" s="10"/>
     </row>
@@ -2673,13 +2678,13 @@
         <v>10</v>
       </c>
       <c r="B68" s="15" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C68" s="15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D68" s="15" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E68" s="10"/>
     </row>
@@ -2689,13 +2694,13 @@
         <v>11</v>
       </c>
       <c r="B69" s="15" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C69" s="15" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D69" s="19" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E69" s="10"/>
     </row>
@@ -2705,13 +2710,13 @@
         <v>12</v>
       </c>
       <c r="B70" s="15" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C70" s="15" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D70" s="19" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E70" s="10"/>
     </row>
@@ -2721,11 +2726,11 @@
         <v>13</v>
       </c>
       <c r="B71" s="15" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C71" s="15"/>
       <c r="D71" s="19" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E71" s="10"/>
     </row>
@@ -2734,16 +2739,16 @@
         <v>14</v>
       </c>
       <c r="B72" s="10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C72" s="10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D72" s="19" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E72" s="10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -2751,13 +2756,13 @@
         <v>15</v>
       </c>
       <c r="B73" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C73" s="10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D73" s="18" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E73" s="10"/>
     </row>
@@ -2766,13 +2771,13 @@
         <v>16</v>
       </c>
       <c r="B74" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C74" s="10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D74" s="18" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E74" s="10"/>
     </row>
@@ -2781,13 +2786,13 @@
         <v>17</v>
       </c>
       <c r="B75" s="15" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C75" s="15" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D75" s="19" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E75" s="10"/>
     </row>

--- a/SUPPLIER RELATED/Phone Book BALAGAN.xlsx
+++ b/SUPPLIER RELATED/Phone Book BALAGAN.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="16600" windowHeight="17020"/>
+    <workbookView windowWidth="12400" windowHeight="17020"/>
   </bookViews>
   <sheets>
     <sheet name="Contact lists" sheetId="1" r:id="rId1"/>
@@ -154,7 +154,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="510">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="513">
   <si>
     <t>BALAGAN RESTO &amp; LOUNGE BAR</t>
   </si>
@@ -718,6 +718,15 @@
   </si>
   <si>
     <t>082266310328</t>
+  </si>
+  <si>
+    <t>Forno (Burger brioche, Croissant)</t>
+  </si>
+  <si>
+    <t>Custom Burger brioche bun, Croissant)</t>
+  </si>
+  <si>
+    <t>+62 877-7324-6834</t>
   </si>
   <si>
     <t>Offers - TG @yesenia_yes</t>
@@ -2605,7 +2614,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2785,20 +2794,17 @@
     <xf numFmtId="0" fontId="9" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3118,7 +3124,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E77"/>
+  <dimension ref="A1:E78"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="5.0859375" style="44" customWidth="1"/>
@@ -3231,7 +3237,7 @@
       <c r="C10" s="52" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="63" t="s">
+      <c r="D10" s="62" t="s">
         <v>18</v>
       </c>
       <c r="E10" s="52"/>
@@ -3294,7 +3300,7 @@
       <c r="C16" s="52" t="s">
         <v>23</v>
       </c>
-      <c r="D16" s="63" t="s">
+      <c r="D16" s="62" t="s">
         <v>24</v>
       </c>
       <c r="E16" s="52" t="s">
@@ -3326,7 +3332,7 @@
       <c r="C18" s="52" t="s">
         <v>30</v>
       </c>
-      <c r="D18" s="63" t="s">
+      <c r="D18" s="62" t="s">
         <v>31</v>
       </c>
       <c r="E18" s="52"/>
@@ -3541,7 +3547,7 @@
       <c r="C34" s="57" t="s">
         <v>65</v>
       </c>
-      <c r="D34" s="64" t="s">
+      <c r="D34" s="63" t="s">
         <v>66</v>
       </c>
       <c r="E34" s="52" t="s">
@@ -3558,7 +3564,7 @@
       <c r="C35" s="57" t="s">
         <v>69</v>
       </c>
-      <c r="D35" s="64" t="s">
+      <c r="D35" s="63" t="s">
         <v>70</v>
       </c>
       <c r="E35" s="52" t="s">
@@ -3575,7 +3581,7 @@
       <c r="C36" s="57" t="s">
         <v>72</v>
       </c>
-      <c r="D36" s="64" t="s">
+      <c r="D36" s="63" t="s">
         <v>73</v>
       </c>
       <c r="E36" s="52" t="s">
@@ -3592,7 +3598,7 @@
       <c r="C37" s="57" t="s">
         <v>75</v>
       </c>
-      <c r="D37" s="64" t="s">
+      <c r="D37" s="63" t="s">
         <v>76</v>
       </c>
       <c r="E37" s="52" t="s">
@@ -3609,7 +3615,7 @@
       <c r="C38" s="57" t="s">
         <v>79</v>
       </c>
-      <c r="D38" s="64" t="s">
+      <c r="D38" s="63" t="s">
         <v>80</v>
       </c>
       <c r="E38" s="52"/>
@@ -3624,7 +3630,7 @@
       <c r="C39" s="57" t="s">
         <v>82</v>
       </c>
-      <c r="D39" s="64" t="s">
+      <c r="D39" s="63" t="s">
         <v>83</v>
       </c>
       <c r="E39" s="52"/>
@@ -3673,7 +3679,7 @@
       <c r="C42" s="57" t="s">
         <v>92</v>
       </c>
-      <c r="D42" s="64" t="s">
+      <c r="D42" s="63" t="s">
         <v>93</v>
       </c>
       <c r="E42" s="52" t="s">
@@ -3724,7 +3730,7 @@
       <c r="C45" s="57" t="s">
         <v>88</v>
       </c>
-      <c r="D45" s="64" t="s">
+      <c r="D45" s="63" t="s">
         <v>101</v>
       </c>
       <c r="E45" s="52" t="s">
@@ -3741,7 +3747,7 @@
       <c r="C46" s="57" t="s">
         <v>103</v>
       </c>
-      <c r="D46" s="64" t="s">
+      <c r="D46" s="63" t="s">
         <v>104</v>
       </c>
       <c r="E46" s="52"/>
@@ -3773,7 +3779,7 @@
       <c r="C48" s="57" t="s">
         <v>88</v>
       </c>
-      <c r="D48" s="64" t="s">
+      <c r="D48" s="63" t="s">
         <v>110</v>
       </c>
       <c r="E48" s="52" t="s">
@@ -3790,7 +3796,7 @@
       <c r="C49" s="57" t="s">
         <v>112</v>
       </c>
-      <c r="D49" s="64" t="s">
+      <c r="D49" s="63" t="s">
         <v>113</v>
       </c>
       <c r="E49" s="52" t="s">
@@ -3807,7 +3813,7 @@
       <c r="C50" s="57" t="s">
         <v>88</v>
       </c>
-      <c r="D50" s="64" t="s">
+      <c r="D50" s="63" t="s">
         <v>116</v>
       </c>
       <c r="E50" s="52" t="s">
@@ -3873,26 +3879,26 @@
       <c r="E54" s="52"/>
     </row>
     <row r="55" spans="1:5">
-      <c r="A55" s="59">
+      <c r="A55" s="56">
         <v>24</v>
       </c>
-      <c r="B55" s="60" t="s">
+      <c r="B55" s="52" t="s">
         <v>128</v>
       </c>
-      <c r="C55" s="60" t="s">
+      <c r="C55" s="52" t="s">
         <v>129</v>
       </c>
-      <c r="D55" s="65" t="s">
+      <c r="D55" s="62" t="s">
         <v>130</v>
       </c>
-      <c r="E55" s="60"/>
+      <c r="E55" s="52"/>
     </row>
     <row r="56" spans="1:5">
-      <c r="A56" s="61"/>
-      <c r="B56" s="61"/>
-      <c r="C56" s="61"/>
-      <c r="D56" s="61"/>
-      <c r="E56" s="61"/>
+      <c r="A56" s="59"/>
+      <c r="B56" s="59"/>
+      <c r="C56" s="59"/>
+      <c r="D56" s="59"/>
+      <c r="E56" s="59"/>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="53" t="s">
@@ -3946,7 +3952,7 @@
       <c r="C60" s="57" t="s">
         <v>137</v>
       </c>
-      <c r="D60" s="64" t="s">
+      <c r="D60" s="63" t="s">
         <v>138</v>
       </c>
       <c r="E60" s="52"/>
@@ -3962,7 +3968,7 @@
       <c r="C61" s="57" t="s">
         <v>140</v>
       </c>
-      <c r="D61" s="64" t="s">
+      <c r="D61" s="63" t="s">
         <v>141</v>
       </c>
       <c r="E61" s="52"/>
@@ -4066,7 +4072,7 @@
       <c r="C67" s="57" t="s">
         <v>160</v>
       </c>
-      <c r="D67" s="64" t="s">
+      <c r="D67" s="63" t="s">
         <v>161</v>
       </c>
       <c r="E67" s="52"/>
@@ -4098,7 +4104,7 @@
       <c r="C69" s="57" t="s">
         <v>166</v>
       </c>
-      <c r="D69" s="64" t="s">
+      <c r="D69" s="63" t="s">
         <v>167</v>
       </c>
       <c r="E69" s="52"/>
@@ -4114,7 +4120,7 @@
       <c r="C70" s="57" t="s">
         <v>169</v>
       </c>
-      <c r="D70" s="64" t="s">
+      <c r="D70" s="63" t="s">
         <v>170</v>
       </c>
       <c r="E70" s="52"/>
@@ -4128,7 +4134,7 @@
         <v>171</v>
       </c>
       <c r="C71" s="57"/>
-      <c r="D71" s="64" t="s">
+      <c r="D71" s="63" t="s">
         <v>172</v>
       </c>
       <c r="E71" s="52"/>
@@ -4143,7 +4149,7 @@
       <c r="C72" s="52" t="s">
         <v>169</v>
       </c>
-      <c r="D72" s="64" t="s">
+      <c r="D72" s="63" t="s">
         <v>174</v>
       </c>
       <c r="E72" s="52" t="s">
@@ -4160,7 +4166,7 @@
       <c r="C73" s="52" t="s">
         <v>176</v>
       </c>
-      <c r="D73" s="63" t="s">
+      <c r="D73" s="62" t="s">
         <v>177</v>
       </c>
       <c r="E73" s="52"/>
@@ -4175,7 +4181,7 @@
       <c r="C74" s="52" t="s">
         <v>176</v>
       </c>
-      <c r="D74" s="63" t="s">
+      <c r="D74" s="62" t="s">
         <v>179</v>
       </c>
       <c r="E74" s="52"/>
@@ -4190,38 +4196,53 @@
       <c r="C75" s="57" t="s">
         <v>181</v>
       </c>
-      <c r="D75" s="64" t="s">
+      <c r="D75" s="63" t="s">
         <v>182</v>
       </c>
       <c r="E75" s="52"/>
     </row>
     <row r="76" spans="1:5">
-      <c r="A76" s="59">
+      <c r="A76" s="56">
         <v>18</v>
       </c>
-      <c r="B76" s="60" t="s">
+      <c r="B76" s="52" t="s">
         <v>183</v>
       </c>
-      <c r="C76" s="60" t="s">
+      <c r="C76" s="52" t="s">
         <v>184</v>
       </c>
-      <c r="D76" s="65" t="s">
+      <c r="D76" s="62" t="s">
         <v>185</v>
       </c>
-      <c r="E76" s="60"/>
+      <c r="E76" s="52"/>
     </row>
     <row r="77" spans="1:5">
-      <c r="A77" s="59">
+      <c r="A77" s="56">
         <v>19</v>
       </c>
-      <c r="B77" s="62" t="s">
+      <c r="B77" s="52" t="s">
         <v>186</v>
       </c>
-      <c r="C77" s="62"/>
-      <c r="D77" s="66" t="s">
+      <c r="C77" s="52"/>
+      <c r="D77" s="62" t="s">
         <v>187</v>
       </c>
-      <c r="E77" s="62"/>
+      <c r="E77" s="52"/>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="60">
+        <v>20</v>
+      </c>
+      <c r="B78" s="61" t="s">
+        <v>188</v>
+      </c>
+      <c r="C78" s="61" t="s">
+        <v>189</v>
+      </c>
+      <c r="D78" s="61" t="s">
+        <v>190</v>
+      </c>
+      <c r="E78" s="61"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -4252,17 +4273,17 @@
   <sheetData>
     <row r="1" ht="20.75" spans="1:26">
       <c r="A1" s="2" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="4"/>
       <c r="D1" s="5" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="E1" s="4"/>
       <c r="F1" s="4"/>
       <c r="G1" s="5" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="H1" s="4"/>
       <c r="I1" s="28"/>
@@ -4289,14 +4310,14 @@
       <c r="B2" s="7"/>
       <c r="C2" s="8"/>
       <c r="D2" s="8" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="E2" s="18" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F2" s="8"/>
       <c r="G2" s="8" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="H2" s="8">
         <v>6287861802079</v>
@@ -4322,7 +4343,7 @@
     </row>
     <row r="3" ht="29.75" spans="1:26">
       <c r="A3" s="9" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B3" s="7"/>
       <c r="C3" s="8"/>
@@ -4330,14 +4351,14 @@
         <v>129</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="F3" s="8"/>
       <c r="G3" s="8" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="I3" s="8"/>
       <c r="J3" s="8"/>
@@ -4360,7 +4381,7 @@
     </row>
     <row r="4" ht="58.75" spans="1:26">
       <c r="A4" s="6" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B4" s="7">
         <v>6287881622313</v>
@@ -4368,11 +4389,11 @@
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
       <c r="E4" s="18" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="F4" s="8"/>
       <c r="G4" s="8" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="H4" s="8">
         <v>6282237077772</v>
@@ -4398,17 +4419,17 @@
     </row>
     <row r="5" ht="17.55" spans="1:26">
       <c r="A5" s="6" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B5" s="7">
         <v>6281934625959</v>
       </c>
       <c r="C5" s="8"/>
       <c r="D5" s="8" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F5" s="8"/>
       <c r="G5" s="8"/>
@@ -4436,17 +4457,17 @@
     </row>
     <row r="6" ht="29.75" spans="1:26">
       <c r="A6" s="6" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B6" s="7">
         <v>6285935247510</v>
       </c>
       <c r="C6" s="8"/>
       <c r="D6" s="8" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="F6" s="8"/>
       <c r="G6" s="8"/>
@@ -4479,10 +4500,10 @@
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="8" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
@@ -4544,14 +4565,14 @@
     </row>
     <row r="9" ht="17.55" spans="1:26">
       <c r="A9" s="6" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C9" s="8"/>
       <c r="D9" s="8" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="E9" s="8">
         <v>62361249490</v>
@@ -4582,21 +4603,21 @@
     </row>
     <row r="10" ht="17.55" spans="1:26">
       <c r="A10" s="6" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C10" s="8"/>
       <c r="D10" s="8" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="E10" s="8">
         <v>6282247504909</v>
       </c>
       <c r="F10" s="8"/>
       <c r="G10" s="8" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="H10" s="8">
         <v>6281246526039</v>
@@ -4623,21 +4644,21 @@
     <row r="11" ht="72.75" spans="1:26">
       <c r="A11" s="6"/>
       <c r="B11" s="7" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C11" s="8"/>
       <c r="D11" s="8" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="E11" s="19" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="F11" s="8"/>
       <c r="G11" s="8" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="H11" s="18" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="I11" s="8"/>
       <c r="J11" s="8"/>
@@ -4660,24 +4681,24 @@
     </row>
     <row r="12" ht="72.75" spans="1:26">
       <c r="A12" s="6" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C12" s="8"/>
       <c r="D12" s="8" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="E12" s="18" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="F12" s="8"/>
       <c r="G12" s="8" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="H12" s="18" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="I12" s="8"/>
       <c r="J12" s="8"/>
@@ -4700,24 +4721,24 @@
     </row>
     <row r="13" ht="29.75" spans="1:26">
       <c r="A13" s="6" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C13" s="8"/>
       <c r="D13" s="8" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="E13" s="8">
         <v>6282151019110</v>
       </c>
       <c r="F13" s="8"/>
       <c r="G13" s="8" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="I13" s="8"/>
       <c r="J13" s="8"/>
@@ -4741,21 +4762,21 @@
     <row r="14" ht="30.5" customHeight="1" spans="1:26">
       <c r="A14" s="6"/>
       <c r="B14" s="10" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C14" s="8"/>
       <c r="D14" s="8" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="F14" s="8"/>
       <c r="G14" s="8" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="I14" s="8"/>
       <c r="J14" s="8"/>
@@ -4782,7 +4803,7 @@
       <c r="C15" s="8"/>
       <c r="D15" s="8"/>
       <c r="E15" s="20" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="F15" s="8"/>
       <c r="G15" s="8"/>
@@ -4812,7 +4833,7 @@
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="13" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="F16" s="8"/>
       <c r="G16" s="8"/>
@@ -4839,21 +4860,21 @@
     <row r="17" ht="58.75" spans="1:26">
       <c r="A17" s="6"/>
       <c r="B17" s="10" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C17" s="8"/>
       <c r="D17" s="8" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="F17" s="8"/>
       <c r="G17" s="8" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="I17" s="8"/>
       <c r="J17" s="8"/>
@@ -4877,21 +4898,21 @@
     <row r="18" ht="44.75" spans="1:26">
       <c r="A18" s="6"/>
       <c r="B18" s="10" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C18" s="8"/>
       <c r="D18" s="8" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="F18" s="8"/>
       <c r="G18" s="8" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="H18" s="18" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="I18" s="8"/>
       <c r="J18" s="8"/>
@@ -4915,21 +4936,21 @@
     <row r="19" ht="72.75" spans="1:26">
       <c r="A19" s="6"/>
       <c r="B19" s="10" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C19" s="8"/>
       <c r="D19" s="8" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="F19" s="8"/>
       <c r="G19" s="8" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="H19" s="19" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="I19" s="8"/>
       <c r="J19" s="8"/>
@@ -4953,18 +4974,18 @@
     <row r="20" ht="29.75" spans="1:26">
       <c r="A20" s="6"/>
       <c r="B20" s="10" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C20" s="8"/>
       <c r="D20" s="8" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="F20" s="8"/>
       <c r="G20" s="8" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="H20" s="21">
         <v>82237077771</v>
@@ -4991,21 +5012,21 @@
     <row r="21" ht="45.5" customHeight="1" spans="1:26">
       <c r="A21" s="6"/>
       <c r="B21" s="10" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C21" s="8"/>
       <c r="D21" s="12" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="E21" s="22" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="F21" s="8"/>
       <c r="G21" s="8" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="H21" s="18" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="I21" s="8"/>
       <c r="J21" s="8"/>
@@ -5031,7 +5052,7 @@
       <c r="B22" s="10"/>
       <c r="C22" s="8"/>
       <c r="D22" s="13" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="E22" s="22"/>
       <c r="F22" s="8"/>
@@ -5058,24 +5079,24 @@
     </row>
     <row r="23" ht="44.75" spans="1:26">
       <c r="A23" s="6" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C23" s="8"/>
       <c r="D23" s="8" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="F23" s="8"/>
       <c r="G23" s="8" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="H23" s="18" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="I23" s="8"/>
       <c r="J23" s="8"/>
@@ -5098,24 +5119,24 @@
     </row>
     <row r="24" ht="101.75" spans="1:26">
       <c r="A24" s="6" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="B24" s="7">
         <v>81339223159</v>
       </c>
       <c r="C24" s="8"/>
       <c r="D24" s="8" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="F24" s="8"/>
       <c r="G24" s="8" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="I24" s="8"/>
       <c r="J24" s="8"/>
@@ -5138,24 +5159,24 @@
     </row>
     <row r="25" ht="58.75" spans="1:26">
       <c r="A25" s="6" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C25" s="8"/>
       <c r="D25" s="8" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="F25" s="8"/>
       <c r="G25" s="8" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="I25" s="8"/>
       <c r="J25" s="8"/>
@@ -5178,21 +5199,21 @@
     </row>
     <row r="26" ht="18.3" customHeight="1" spans="1:26">
       <c r="A26" s="6" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="B26" s="7">
         <v>831156174540</v>
       </c>
       <c r="C26" s="8"/>
       <c r="D26" s="8" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="F26" s="8"/>
       <c r="G26" s="8" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="H26" s="12">
         <v>6282340074616</v>
@@ -5225,7 +5246,7 @@
       <c r="F27" s="8"/>
       <c r="G27" s="8"/>
       <c r="H27" s="13" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="I27" s="8"/>
       <c r="J27" s="8"/>
@@ -5248,20 +5269,20 @@
     </row>
     <row r="28" ht="29.75" spans="1:26">
       <c r="A28" s="6" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
       <c r="E28" s="8"/>
       <c r="F28" s="8"/>
       <c r="G28" s="8" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="H28" s="8" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="I28" s="8"/>
       <c r="J28" s="8"/>
@@ -5284,20 +5305,20 @@
     </row>
     <row r="29" ht="88.5" customHeight="1" spans="1:26">
       <c r="A29" s="6" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C29" s="8"/>
       <c r="D29" s="8"/>
       <c r="E29" s="8"/>
       <c r="F29" s="8"/>
       <c r="G29" s="12" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="H29" s="18" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="I29" s="8"/>
       <c r="J29" s="8"/>
@@ -5326,7 +5347,7 @@
       <c r="E30" s="8"/>
       <c r="F30" s="8"/>
       <c r="G30" s="13" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="H30" s="18"/>
       <c r="I30" s="8"/>
@@ -5350,19 +5371,19 @@
     </row>
     <row r="31" ht="20.75" spans="1:26">
       <c r="A31" s="6" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C31" s="8"/>
       <c r="D31" s="14" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="E31" s="8"/>
       <c r="F31" s="8"/>
       <c r="G31" s="8" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="H31" s="21">
         <v>6285101729494</v>
@@ -5388,24 +5409,24 @@
     </row>
     <row r="32" ht="58.75" spans="1:26">
       <c r="A32" s="6" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C32" s="8"/>
       <c r="D32" s="8" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="E32" s="8">
         <v>6281246288922</v>
       </c>
       <c r="F32" s="8"/>
       <c r="G32" s="8" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="H32" s="8" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="I32" s="8"/>
       <c r="J32" s="8"/>
@@ -5428,21 +5449,21 @@
     </row>
     <row r="33" ht="45.5" customHeight="1" spans="1:26">
       <c r="A33" s="6" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="C33" s="8"/>
       <c r="D33" s="12" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="E33" s="22" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="F33" s="8"/>
       <c r="G33" s="8" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="H33" s="21">
         <v>82340619759</v>
@@ -5471,7 +5492,7 @@
       <c r="B34" s="7"/>
       <c r="C34" s="8"/>
       <c r="D34" s="13" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="E34" s="22"/>
       <c r="F34" s="8"/>
@@ -5498,24 +5519,24 @@
     </row>
     <row r="35" ht="58.75" spans="1:26">
       <c r="A35" s="6" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="C35" s="8"/>
       <c r="D35" s="8" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="F35" s="8"/>
       <c r="G35" s="8" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H35" s="8" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="I35" s="8"/>
       <c r="J35" s="8"/>
@@ -5538,24 +5559,24 @@
     </row>
     <row r="36" ht="29.75" spans="1:26">
       <c r="A36" s="6" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="C36" s="8"/>
       <c r="D36" s="8" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="E36" s="8" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="F36" s="8"/>
       <c r="G36" s="8" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="H36" s="8" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="I36" s="8"/>
       <c r="J36" s="8"/>
@@ -5578,24 +5599,24 @@
     </row>
     <row r="37" ht="58.75" spans="1:26">
       <c r="A37" s="6" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="B37" s="15">
         <v>628113893177</v>
       </c>
       <c r="C37" s="8"/>
       <c r="D37" s="8" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F37" s="8"/>
       <c r="G37" s="8" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="H37" s="23" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="I37" s="8"/>
       <c r="J37" s="8"/>
@@ -5618,19 +5639,19 @@
     </row>
     <row r="38" ht="29.75" spans="1:26">
       <c r="A38" s="6" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="B38" s="15" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="C38" s="8"/>
       <c r="D38" s="8"/>
       <c r="E38" s="8" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="F38" s="8"/>
       <c r="G38" s="8" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="H38" s="24">
         <v>6285738213689</v>
@@ -5656,17 +5677,17 @@
     </row>
     <row r="39" ht="43" customHeight="1" spans="1:26">
       <c r="A39" s="6" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C39" s="8"/>
       <c r="D39" s="16" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="E39" s="25" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="F39" s="8"/>
       <c r="G39" s="8"/>
@@ -5696,7 +5717,7 @@
       <c r="C40" s="8"/>
       <c r="D40" s="16"/>
       <c r="E40" s="26" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="F40" s="8"/>
       <c r="G40" s="8"/>
@@ -5722,17 +5743,17 @@
     </row>
     <row r="41" ht="44.75" spans="1:26">
       <c r="A41" s="6" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C41" s="8"/>
       <c r="D41" s="8" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="F41" s="8"/>
       <c r="G41" s="8"/>
@@ -5758,17 +5779,17 @@
     </row>
     <row r="42" ht="59.5" customHeight="1" spans="1:26">
       <c r="A42" s="6" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C42" s="8"/>
       <c r="D42" s="8" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="E42" s="12" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="F42" s="8"/>
       <c r="G42" s="8"/>
@@ -5798,7 +5819,7 @@
       <c r="C43" s="8"/>
       <c r="D43" s="8"/>
       <c r="E43" s="20" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="F43" s="8"/>
       <c r="G43" s="8"/>
@@ -5828,7 +5849,7 @@
       <c r="C44" s="8"/>
       <c r="D44" s="8"/>
       <c r="E44" s="20" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="F44" s="8"/>
       <c r="G44" s="8"/>
@@ -5858,7 +5879,7 @@
       <c r="C45" s="8"/>
       <c r="D45" s="8"/>
       <c r="E45" s="20" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="F45" s="8"/>
       <c r="G45" s="8"/>
@@ -5888,7 +5909,7 @@
       <c r="C46" s="8"/>
       <c r="D46" s="8"/>
       <c r="E46" s="13" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="F46" s="8"/>
       <c r="G46" s="8"/>
@@ -5914,17 +5935,17 @@
     </row>
     <row r="47" ht="29.75" spans="1:26">
       <c r="A47" s="6" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="B47" s="17" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="C47" s="8"/>
       <c r="D47" s="8" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="E47" s="22" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="F47" s="8"/>
       <c r="G47" s="8"/>
@@ -5950,17 +5971,17 @@
     </row>
     <row r="48" ht="29.75" spans="1:26">
       <c r="A48" s="6" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="B48" s="17" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="C48" s="8"/>
       <c r="D48" s="8" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="E48" s="8" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="F48" s="8"/>
       <c r="G48" s="8"/>
@@ -5986,17 +6007,17 @@
     </row>
     <row r="49" ht="29.75" spans="1:26">
       <c r="A49" s="6" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="B49" s="11" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="C49" s="8"/>
       <c r="D49" s="8" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="F49" s="8"/>
       <c r="G49" s="8"/>
@@ -6056,7 +6077,7 @@
       <c r="E51" s="8"/>
       <c r="F51" s="8"/>
       <c r="G51" s="14" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="H51" s="8"/>
       <c r="I51" s="8"/>
@@ -6086,7 +6107,7 @@
       <c r="E52" s="8"/>
       <c r="F52" s="8"/>
       <c r="G52" s="8" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="H52" s="8">
         <v>628563845123</v>
@@ -6112,7 +6133,7 @@
     </row>
     <row r="53" ht="58.75" spans="1:26">
       <c r="A53" s="9" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="B53" s="7"/>
       <c r="C53" s="8"/>
@@ -6120,10 +6141,10 @@
       <c r="E53" s="8"/>
       <c r="F53" s="8"/>
       <c r="G53" s="8" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="H53" s="18" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="I53" s="8"/>
       <c r="J53" s="8"/>
@@ -6146,19 +6167,19 @@
     </row>
     <row r="54" ht="20.75" spans="1:26">
       <c r="A54" s="6" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B54" s="7">
         <v>79031453510</v>
       </c>
       <c r="C54" s="8"/>
       <c r="D54" s="14" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="E54" s="8"/>
       <c r="F54" s="8"/>
       <c r="G54" s="8" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="H54" s="8">
         <v>6281338228694</v>
@@ -6189,14 +6210,14 @@
       </c>
       <c r="C55" s="8"/>
       <c r="D55" s="8" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="E55" s="18" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="F55" s="8"/>
       <c r="G55" s="8" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="H55" s="8">
         <v>6281337343188</v>
@@ -6227,14 +6248,14 @@
       </c>
       <c r="C56" s="8"/>
       <c r="D56" s="8" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="E56" s="18" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="F56" s="8"/>
       <c r="G56" s="8" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="H56" s="8">
         <v>6287860119196</v>
@@ -6260,21 +6281,21 @@
     </row>
     <row r="57" ht="101.75" spans="1:26">
       <c r="A57" s="6" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="C57" s="8"/>
       <c r="D57" s="8" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="E57" s="27" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="F57" s="8"/>
       <c r="G57" s="8" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="H57" s="8">
         <v>6282144056477</v>
@@ -6300,24 +6321,24 @@
     </row>
     <row r="58" ht="72.75" spans="1:26">
       <c r="A58" s="6" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="C58" s="8"/>
       <c r="D58" s="8" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="E58" s="19" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="F58" s="8"/>
       <c r="G58" s="8" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="H58" s="8" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="I58" s="8"/>
       <c r="J58" s="8"/>
@@ -6340,22 +6361,22 @@
     </row>
     <row r="59" ht="44.75" spans="1:26">
       <c r="A59" s="6" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="B59" s="7">
         <v>89605256772</v>
       </c>
       <c r="C59" s="8"/>
       <c r="D59" s="8" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="E59" s="18" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="F59" s="8"/>
       <c r="G59" s="8"/>
       <c r="H59" s="8" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="I59" s="8"/>
       <c r="J59" s="8"/>
@@ -6378,24 +6399,24 @@
     </row>
     <row r="60" ht="72.75" spans="1:26">
       <c r="A60" s="6" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="B60" s="7">
         <v>628123853990</v>
       </c>
       <c r="C60" s="8"/>
       <c r="D60" s="8" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="E60" s="18" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="F60" s="8"/>
       <c r="G60" s="8" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="H60" s="8" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="I60" s="8"/>
       <c r="J60" s="8"/>
@@ -6418,24 +6439,24 @@
     </row>
     <row r="61" ht="44.75" spans="1:26">
       <c r="A61" s="6" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="B61" s="10" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="C61" s="8"/>
       <c r="D61" s="8" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="E61" s="18" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="F61" s="8"/>
       <c r="G61" s="8" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="H61" s="8" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="I61" s="8"/>
       <c r="J61" s="8"/>
@@ -6459,21 +6480,21 @@
     <row r="62" ht="58.75" spans="1:26">
       <c r="A62" s="6"/>
       <c r="B62" s="7" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="C62" s="8"/>
       <c r="D62" s="8" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="E62" s="18" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="F62" s="8"/>
       <c r="G62" s="8" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="H62" s="18" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="I62" s="8"/>
       <c r="J62" s="8"/>
@@ -6496,24 +6517,24 @@
     </row>
     <row r="63" ht="58.75" spans="1:26">
       <c r="A63" s="6" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="B63" s="10" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="C63" s="8"/>
       <c r="D63" s="8" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="E63" s="18" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="F63" s="8"/>
       <c r="G63" s="8" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="H63" s="8" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="I63" s="8"/>
       <c r="J63" s="8"/>
@@ -6536,24 +6557,24 @@
     </row>
     <row r="64" ht="44.75" spans="1:26">
       <c r="A64" s="6" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="C64" s="8"/>
       <c r="D64" s="8" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="E64" s="18" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="F64" s="8"/>
       <c r="G64" s="8" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="H64" s="8" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="I64" s="8"/>
       <c r="J64" s="8"/>
@@ -6576,7 +6597,7 @@
     </row>
     <row r="65" ht="29.75" spans="1:26">
       <c r="A65" s="6" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="B65" s="7">
         <v>6281320191717</v>
@@ -6586,10 +6607,10 @@
       <c r="E65" s="8"/>
       <c r="F65" s="8"/>
       <c r="G65" s="8" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="H65" s="8" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="I65" s="8"/>
       <c r="J65" s="8"/>
@@ -6612,20 +6633,20 @@
     </row>
     <row r="66" ht="44.75" spans="1:26">
       <c r="A66" s="6" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="B66" s="10" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="C66" s="8"/>
       <c r="D66" s="8"/>
       <c r="E66" s="8"/>
       <c r="F66" s="8"/>
       <c r="G66" s="8" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="H66" s="8" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="I66" s="8"/>
       <c r="J66" s="8"/>
@@ -6648,20 +6669,20 @@
     </row>
     <row r="67" ht="59.5" customHeight="1" spans="1:26">
       <c r="A67" s="6" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="C67" s="8"/>
       <c r="D67" s="8"/>
       <c r="E67" s="8"/>
       <c r="F67" s="8"/>
       <c r="G67" s="8" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="H67" s="38" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="I67" s="8"/>
       <c r="J67" s="8"/>
@@ -6691,7 +6712,7 @@
       <c r="F68" s="8"/>
       <c r="G68" s="8"/>
       <c r="H68" s="20" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="I68" s="8"/>
       <c r="J68" s="8"/>
@@ -6721,7 +6742,7 @@
       <c r="F69" s="8"/>
       <c r="G69" s="8"/>
       <c r="H69" s="13" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="I69" s="8"/>
       <c r="J69" s="8"/>
@@ -6744,17 +6765,17 @@
     </row>
     <row r="70" ht="29.75" spans="1:26">
       <c r="A70" s="6" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C70" s="8"/>
       <c r="D70" s="8"/>
       <c r="E70" s="8"/>
       <c r="F70" s="8"/>
       <c r="G70" s="8" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="H70" s="21">
         <v>81232382755</v>
@@ -6780,21 +6801,21 @@
     </row>
     <row r="71" ht="29.75" spans="1:26">
       <c r="A71" s="6" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="B71" s="11" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="C71" s="8"/>
       <c r="D71" s="8" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E71" s="8">
         <v>87801791517</v>
       </c>
       <c r="F71" s="8"/>
       <c r="G71" s="8" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="H71" s="21">
         <v>81239623698</v>
@@ -6820,21 +6841,21 @@
     </row>
     <row r="72" ht="17.55" spans="1:26">
       <c r="A72" s="6" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="B72" s="7" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C72" s="8"/>
       <c r="D72" s="8" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="E72" s="8">
         <v>81936003868</v>
       </c>
       <c r="F72" s="8"/>
       <c r="G72" s="8" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="H72" s="21">
         <v>82339733332</v>
@@ -6861,18 +6882,18 @@
     <row r="73" ht="17.55" spans="1:26">
       <c r="A73" s="6"/>
       <c r="B73" s="11" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C73" s="8"/>
       <c r="D73" s="8" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="E73" s="8">
         <v>81238666563</v>
       </c>
       <c r="F73" s="8"/>
       <c r="G73" s="8" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="H73" s="21">
         <v>82146558362</v>
@@ -6898,24 +6919,24 @@
     </row>
     <row r="74" ht="44.75" spans="1:26">
       <c r="A74" s="6" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="B74" s="11" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="C74" s="8"/>
       <c r="D74" s="8" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="E74" s="8">
         <v>82247504909</v>
       </c>
       <c r="F74" s="8"/>
       <c r="G74" s="8" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="H74" s="19" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="I74" s="8"/>
       <c r="J74" s="8"/>
@@ -6938,17 +6959,17 @@
     </row>
     <row r="75" ht="29.75" spans="1:26">
       <c r="A75" s="6" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="B75" s="11" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="C75" s="8"/>
       <c r="D75" s="8"/>
       <c r="E75" s="8"/>
       <c r="F75" s="8"/>
       <c r="G75" s="8" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="H75" s="21">
         <v>82237077771</v>
@@ -6974,20 +6995,20 @@
     </row>
     <row r="76" ht="58.75" spans="1:26">
       <c r="A76" s="6" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="B76" s="10" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="C76" s="8"/>
       <c r="D76" s="8"/>
       <c r="E76" s="8"/>
       <c r="F76" s="8"/>
       <c r="G76" s="8" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="H76" s="18" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="I76" s="8"/>
       <c r="J76" s="8"/>
@@ -7010,20 +7031,20 @@
     </row>
     <row r="77" ht="29.75" spans="1:26">
       <c r="A77" s="6" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="B77" s="10" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="C77" s="8"/>
       <c r="D77" s="8"/>
       <c r="E77" s="8"/>
       <c r="F77" s="8"/>
       <c r="G77" s="8" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="H77" s="8" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="I77" s="8"/>
       <c r="J77" s="8"/>
@@ -7046,7 +7067,7 @@
     </row>
     <row r="78" ht="29.75" spans="1:26">
       <c r="A78" s="6" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="B78" s="7"/>
       <c r="C78" s="8"/>
@@ -7054,10 +7075,10 @@
       <c r="E78" s="8"/>
       <c r="F78" s="8"/>
       <c r="G78" s="8" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="H78" s="8" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="I78" s="8"/>
       <c r="J78" s="8"/>
@@ -7080,20 +7101,20 @@
     </row>
     <row r="79" ht="29.75" spans="1:26">
       <c r="A79" s="6" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="B79" s="10" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="C79" s="8"/>
       <c r="D79" s="8"/>
       <c r="E79" s="8"/>
       <c r="F79" s="8"/>
       <c r="G79" s="8" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="H79" s="8" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="I79" s="8"/>
       <c r="J79" s="8"/>
@@ -7116,20 +7137,20 @@
     </row>
     <row r="80" ht="29.75" spans="1:26">
       <c r="A80" s="6" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="B80" s="7" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="C80" s="8"/>
       <c r="D80" s="8"/>
       <c r="E80" s="8"/>
       <c r="F80" s="8"/>
       <c r="G80" s="8" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="H80" s="8" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="I80" s="8"/>
       <c r="J80" s="8"/>
@@ -7152,20 +7173,20 @@
     </row>
     <row r="81" ht="116.75" spans="1:26">
       <c r="A81" s="6" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="B81" s="7" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="C81" s="8"/>
       <c r="D81" s="8"/>
       <c r="E81" s="8"/>
       <c r="F81" s="8"/>
       <c r="G81" s="8" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="H81" s="18" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="I81" s="8"/>
       <c r="J81" s="8"/>
@@ -7188,7 +7209,7 @@
     </row>
     <row r="82" ht="17.55" spans="1:26">
       <c r="A82" s="6" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="B82" s="7">
         <v>81391278684</v>
@@ -7198,7 +7219,7 @@
       <c r="E82" s="8"/>
       <c r="F82" s="8"/>
       <c r="G82" s="8" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="H82" s="21">
         <v>811351678</v>
@@ -7224,7 +7245,7 @@
     </row>
     <row r="83" ht="29.75" spans="1:26">
       <c r="A83" s="6" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="B83" s="7">
         <v>82144952073</v>
@@ -7234,10 +7255,10 @@
       <c r="E83" s="8"/>
       <c r="F83" s="8"/>
       <c r="G83" s="8" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="H83" s="8" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="I83" s="8"/>
       <c r="J83" s="8"/>
@@ -7260,20 +7281,20 @@
     </row>
     <row r="84" ht="29.75" spans="1:26">
       <c r="A84" s="6" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="B84" s="10" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="C84" s="8"/>
       <c r="D84" s="8"/>
       <c r="E84" s="8"/>
       <c r="F84" s="8"/>
       <c r="G84" s="8" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="H84" s="8" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="I84" s="8"/>
       <c r="J84" s="8"/>
@@ -7296,20 +7317,20 @@
     </row>
     <row r="85" ht="29.75" spans="1:26">
       <c r="A85" s="6" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="B85" s="7" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="C85" s="8"/>
       <c r="D85" s="8"/>
       <c r="E85" s="8"/>
       <c r="F85" s="8"/>
       <c r="G85" s="8" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="H85" s="8" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="I85" s="8"/>
       <c r="J85" s="8"/>
@@ -7332,20 +7353,20 @@
     </row>
     <row r="86" ht="160.5" customHeight="1" spans="1:26">
       <c r="A86" s="6" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="B86" s="7" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="C86" s="8"/>
       <c r="D86" s="8"/>
       <c r="E86" s="8"/>
       <c r="F86" s="8"/>
       <c r="G86" s="12" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="H86" s="8" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="I86" s="8"/>
       <c r="J86" s="8"/>
@@ -7374,7 +7395,7 @@
       <c r="E87" s="8"/>
       <c r="F87" s="8"/>
       <c r="G87" s="13" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="H87" s="8"/>
       <c r="I87" s="8"/>
@@ -7398,10 +7419,10 @@
     </row>
     <row r="88" ht="29.75" spans="1:26">
       <c r="A88" s="6" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="B88" s="7" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="C88" s="8"/>
       <c r="D88" s="8"/>
@@ -7430,10 +7451,10 @@
     </row>
     <row r="89" ht="17.55" spans="1:26">
       <c r="A89" s="6" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="B89" s="7" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="C89" s="8"/>
       <c r="D89" s="8"/>
@@ -7462,10 +7483,10 @@
     </row>
     <row r="90" ht="17.55" spans="1:26">
       <c r="A90" s="6" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="B90" s="10" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="C90" s="8"/>
       <c r="D90" s="8"/>
@@ -7494,10 +7515,10 @@
     </row>
     <row r="91" ht="17.55" spans="1:26">
       <c r="A91" s="6" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="B91" s="7" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="C91" s="8"/>
       <c r="D91" s="8"/>
@@ -7526,10 +7547,10 @@
     </row>
     <row r="92" ht="17.55" spans="1:26">
       <c r="A92" s="6" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="B92" s="7" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="C92" s="8"/>
       <c r="D92" s="8"/>
@@ -7558,10 +7579,10 @@
     </row>
     <row r="93" ht="127.2" customHeight="1" spans="1:26">
       <c r="A93" s="6" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="B93" s="31" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="C93" s="8"/>
       <c r="D93" s="8"/>
@@ -7618,10 +7639,10 @@
     </row>
     <row r="95" ht="29.75" spans="1:26">
       <c r="A95" s="6" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="B95" s="11" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="C95" s="8"/>
       <c r="D95" s="8"/>
@@ -7650,10 +7671,10 @@
     </row>
     <row r="96" ht="17.55" spans="1:26">
       <c r="A96" s="6" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="B96" s="7" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="C96" s="8"/>
       <c r="D96" s="8"/>
@@ -7682,10 +7703,10 @@
     </row>
     <row r="97" ht="17.55" spans="1:26">
       <c r="A97" s="6" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="B97" s="7" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="C97" s="8"/>
       <c r="D97" s="8"/>
@@ -7714,10 +7735,10 @@
     </row>
     <row r="98" ht="17.55" spans="1:26">
       <c r="A98" s="6" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="B98" s="7" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="C98" s="8"/>
       <c r="D98" s="8"/>
@@ -7746,7 +7767,7 @@
     </row>
     <row r="99" ht="17.55" spans="1:26">
       <c r="A99" s="6" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="B99" s="7">
         <v>87766749080</v>
@@ -7778,10 +7799,10 @@
     </row>
     <row r="100" ht="17.55" spans="1:26">
       <c r="A100" s="6" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="B100" s="7" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="C100" s="8"/>
       <c r="D100" s="8"/>
@@ -7810,10 +7831,10 @@
     </row>
     <row r="101" ht="29.75" spans="1:26">
       <c r="A101" s="6" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="B101" s="7" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="C101" s="8"/>
       <c r="D101" s="8"/>
@@ -7842,10 +7863,10 @@
     </row>
     <row r="102" ht="79.15" customHeight="1" spans="1:26">
       <c r="A102" s="33" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="B102" s="34" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="C102" s="8"/>
       <c r="D102" s="8"/>
@@ -7875,7 +7896,7 @@
     <row r="103" ht="17.55" spans="1:26">
       <c r="A103" s="33"/>
       <c r="B103" s="35" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="C103" s="8"/>
       <c r="D103" s="8"/>
@@ -7933,7 +7954,7 @@
     <row r="105" ht="17.55" spans="1:26">
       <c r="A105" s="33"/>
       <c r="B105" s="35" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="C105" s="8"/>
       <c r="D105" s="8"/>
@@ -7963,7 +7984,7 @@
     <row r="106" ht="17.55" spans="1:26">
       <c r="A106" s="33"/>
       <c r="B106" s="37" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="C106" s="8"/>
       <c r="D106" s="8"/>
@@ -7992,10 +8013,10 @@
     </row>
     <row r="107" ht="17.55" spans="1:26">
       <c r="A107" s="6" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="B107" s="7" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="C107" s="8"/>
       <c r="D107" s="8"/>
@@ -8024,10 +8045,10 @@
     </row>
     <row r="108" ht="29.75" spans="1:26">
       <c r="A108" s="6" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="B108" s="10" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="C108" s="8"/>
       <c r="D108" s="8"/>
@@ -8056,10 +8077,10 @@
     </row>
     <row r="109" ht="17.55" spans="1:26">
       <c r="A109" s="6" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="B109" s="7" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="C109" s="8"/>
       <c r="D109" s="8"/>
@@ -8088,10 +8109,10 @@
     </row>
     <row r="110" ht="17.55" spans="1:26">
       <c r="A110" s="6" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="B110" s="7" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="C110" s="8"/>
       <c r="D110" s="8"/>
@@ -8120,10 +8141,10 @@
     </row>
     <row r="111" ht="17.55" spans="1:26">
       <c r="A111" s="6" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="B111" s="7" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="C111" s="8"/>
       <c r="D111" s="8"/>
